--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -283,7 +283,7 @@
 4. Click "Purchase"</t>
   </si>
   <si>
-    <t>Name="Bumblebee QA", Card="4111111111111111", Month="12", Year="2030"</t>
+    <t>Name="QA Automation", Card="4111111111111111", Month="12", Year="2030"</t>
   </si>
   <si>
     <t>A confirmation dialog reads "Thank you for your purchase!" and shows an Id, Amount, Card Number, Name and Date matching the input</t>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -243,7 +243,7 @@
 3. Add it to the cart again</t>
   </si>
   <si>
-    <t>Same product added twice</t>
+    <t>"Samsung galaxy s6", added twice</t>
   </si>
   <si>
     <t>Two separate rows appear for the product -- NOT a single row with quantity = 2</t>
@@ -258,11 +258,15 @@
     <t>Delete an item from the cart</t>
   </si>
   <si>
-    <t>At least one item is in the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Cart page
-2. Click "Delete" on a row</t>
+    <t>None (test adds the item itself, then deletes it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a product detail page and add it to the cart
+2. Open the Cart page
+3. Click "Delete" on that row</t>
+  </si>
+  <si>
+    <t>"Nexus 6"</t>
   </si>
   <si>
     <t>The row is removed from the table without a page reload</t>
@@ -274,36 +278,38 @@
     <t>Place an order with all fields filled correctly</t>
   </si>
   <si>
-    <t>The cart contains at least one item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Cart page
-2. Click "Place Order"
-3. Fill Name, Country, City, Credit card, Month, Year
+    <t>None (test adds the item itself)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a product detail page and add it to the cart
+2. Open the Cart page
+3. Click "Place Order"
+4. Fill Name, Country, City, Credit card, Month, Year
+5. Click "Purchase"</t>
+  </si>
+  <si>
+    <t>Product="Nokia lumia 1520"; Name="QA Automation", Country="Vietnam", City="Ho Chi Minh City", Card="4111111111111111", Month="12", Year="2030"</t>
+  </si>
+  <si>
+    <t>A confirmation dialog reads "Thank you for your purchase!" and shows an Id, Amount, Card Number, Name and Date matching the input</t>
+  </si>
+  <si>
+    <t>Verified live. Selector note: the "Place Order" button must be matched by role/exact text, not a bare substring locator -- it otherwise ambiguously matches the order modal's own heading, "Place order".</t>
+  </si>
+  <si>
+    <t>CART-005</t>
+  </si>
+  <si>
+    <t>Submit the order form with every field left empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Open a product detail page and add it to the cart
+2. Open the Cart page and click "Place Order"
+3. Leave every field empty
 4. Click "Purchase"</t>
   </si>
   <si>
-    <t>Name="QA Automation", Card="4111111111111111", Month="12", Year="2030"</t>
-  </si>
-  <si>
-    <t>A confirmation dialog reads "Thank you for your purchase!" and shows an Id, Amount, Card Number, Name and Date matching the input</t>
-  </si>
-  <si>
-    <t>Verified live. Selector note: the "Place Order" button must be matched by role/exact text, not a bare substring locator -- it otherwise ambiguously matches the order modal's own heading, "Place order".</t>
-  </si>
-  <si>
-    <t>CART-005</t>
-  </si>
-  <si>
-    <t>Submit the order form with every field left empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open "Place Order"
-2. Leave every field empty
-3. Click "Purchase"</t>
-  </si>
-  <si>
-    <t>All fields = ""</t>
+    <t>Product="Nokia lumia 1520"; all order-form fields = ""</t>
   </si>
   <si>
     <t>No confirmation dialog appears</t>
@@ -318,12 +324,13 @@
     <t>Submit the order form with only the Name field filled</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open "Place Order"
-2. Fill only the Name field
-3. Click "Purchase"</t>
-  </si>
-  <si>
-    <t>Name="Only Name Filled"; all other fields empty</t>
+    <t xml:space="preserve">1. Open a product detail page and add it to the cart
+2. Open the Cart page and click "Place Order"
+3. Fill only the Name field
+4. Click "Purchase"</t>
+  </si>
+  <si>
+    <t>Product="Nexus 6"; Name="Only Name Filled"; all other fields empty</t>
   </si>
   <si>
     <t>No confirmation dialog appears (same silent no-op as CART-005)</t>
@@ -338,12 +345,13 @@
     <t>Submit the order form with only the Name field left empty</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open "Place Order"
-2. Fill Country, City, Card, Month, Year but leave Name empty
-3. Click "Purchase"</t>
-  </si>
-  <si>
-    <t>Name=""; all other fields filled with valid values</t>
+    <t xml:space="preserve">1. Open a product detail page and add it to the cart
+2. Open the Cart page and click "Place Order"
+3. Fill Country, City, Card, Month, Year but leave Name empty
+4. Click "Purchase"</t>
+  </si>
+  <si>
+    <t>Product="Nexus 6"; Name=""; Country="Vietnam", City="Ho Chi Minh City", Card="4111111111111111", Month="12", Year="2030"</t>
   </si>
   <si>
     <t>No confirmation dialog appears -- Name specifically is required</t>
@@ -358,16 +366,14 @@
     <t>Attempt to place an order with a non-numeric credit card value</t>
   </si>
   <si>
-    <t>The cart contains at least one item; other fields filled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open "Place Order"
-2. Fill Card with a non-numeric string (e.g. "abcd")
-3. Fill remaining fields
-4. Click "Purchase"</t>
-  </si>
-  <si>
-    <t>Card="abcd"</t>
+    <t xml:space="preserve">1. Open a product detail page and add it to the cart
+2. Open the Cart page and click "Place Order"
+3. Fill Card with a non-numeric string (e.g. "abcd")
+4. Fill remaining fields
+5. Click "Purchase"</t>
+  </si>
+  <si>
+    <t>Product="Nokia lumia 1520"; Name="QA Automation", Country="Vietnam", City="Ho Chi Minh City", Card="abcd", Month="12", Year="2030"</t>
   </si>
   <si>
     <t>Purchase SUCCEEDS regardless -- the confirmation dialog shows "Card Number: abcd" verbatim. There is no card-format validation at all.</t>
@@ -1132,10 +1138,10 @@
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>17</v>
@@ -1143,10 +1149,10 @@
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
@@ -1155,27 +1161,27 @@
         <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -1184,27 +1190,27 @@
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
@@ -1213,27 +1219,27 @@
         <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1242,27 +1248,27 @@
         <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
@@ -1271,7 +1277,7 @@
         <v>55</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>106</v>
